--- a/Outputs/Scenarios/PtX_demand_FI_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_FI_Electrification.xlsx
@@ -1555,7 +1555,7 @@
         <v>0.003033729486396468</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0397159707731828</v>
+        <v>0.03971597077318279</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.006619328462197134</v>
+        <v>0.006619328462197133</v>
       </c>
     </row>
     <row r="32">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.0397159707731828</v>
+        <v>0.03971597077318279</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>0.0001596699729682351</v>
       </c>
       <c r="K42" t="n">
-        <v>0.006619328462197134</v>
+        <v>0.006619328462197133</v>
       </c>
     </row>
     <row r="43">

--- a/Outputs/Scenarios/PtX_demand_FI_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_FI_Electrification.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.002049293468758665</v>
       </c>
       <c r="K16" t="n">
-        <v>0.006748400895309333</v>
+        <v>0.007225934957707601</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.001124733482551556</v>
+        <v>0.001485837450392948</v>
       </c>
     </row>
     <row r="18">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.004498933930206222</v>
+        <v>0.005943349801571791</v>
       </c>
     </row>
     <row r="19">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.006748400895309333</v>
+        <v>0.005943349801571791</v>
       </c>
     </row>
     <row r="20">
@@ -1333,7 +1333,7 @@
         <v>0.0001642307607606403</v>
       </c>
       <c r="K24" t="n">
-        <v>0.009359041386837475</v>
+        <v>0.009188308584105555</v>
       </c>
     </row>
     <row r="25">
@@ -1370,7 +1370,7 @@
         <v>0.0009940891403961442</v>
       </c>
       <c r="K25" t="n">
-        <v>0.09145507372905402</v>
+        <v>0.08978669975607687</v>
       </c>
     </row>
     <row r="26">
@@ -1481,7 +1481,7 @@
         <v>2.952685001275128e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.001124733482551556</v>
+        <v>0.001485837450392948</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.003033729486396468</v>
       </c>
       <c r="K30" t="n">
-        <v>0.03971597077318279</v>
+        <v>0.03898492122940409</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.006619328462197133</v>
+        <v>0.00801629910901443</v>
       </c>
     </row>
     <row r="32">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.02647731384878853</v>
+        <v>0.03206519643605772</v>
       </c>
     </row>
     <row r="33">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.03971597077318279</v>
+        <v>0.03206519643605772</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>0.0001596699729682351</v>
       </c>
       <c r="K42" t="n">
-        <v>0.006619328462197133</v>
+        <v>0.00801629910901443</v>
       </c>
     </row>
     <row r="43">
